--- a/Documentazione/Template/Consuntivi.xlsx
+++ b/Documentazione/Template/Consuntivi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y.dacco\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tsspa-my.sharepoint.com/personal/y_dacco_teamsystem_com/Documents/Documenti/Claude/Projects/Yanko_e_Fede/Projexa/Documentazione/Template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCAFEF8-74D5-4D03-958B-EC5001EAF63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{0BCAFEF8-74D5-4D03-958B-EC5001EAF63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9EC289D-A308-4471-A341-C313D8FDFD62}"/>
   <bookViews>
     <workbookView xWindow="51480" yWindow="2535" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
     <author>Yanko Dacco'</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{21712D9C-0AB4-433D-8991-A29E5862D920}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{21712D9C-0AB4-433D-8991-A29E5862D920}">
       <text>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Nome Dipendente</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>mario.rossi@projexa.it</t>
+  </si>
+  <si>
+    <t>Data Attivita</t>
   </si>
 </sst>
 </file>
@@ -180,13 +183,13 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -203,10 +206,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,196 +495,220 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="24.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>46023</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>3</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E4" s="1"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E5" s="1"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E6" s="1"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E7" s="1"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E8" s="1"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E9" s="1"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E10" s="1"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E11" s="1"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E12" s="1"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E13" s="1"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E15" s="1"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E16" s="1"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E17" s="1"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E18" s="1"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{7868BA0D-99DD-4E04-9494-23D9F637803F}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{7868BA0D-99DD-4E04-9494-23D9F637803F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId2"/>
